--- a/docs/资产清单_v3_可导入.xlsx
+++ b/docs/资产清单_v3_可导入.xlsx
@@ -8,18 +8,24 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口资产" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据资产" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域属性表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能资产" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支持资产" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STRIDE映射表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="边界接口表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据资产" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="域属性表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能资产" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支持资产" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STRIDE映射表" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信任边界表" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="威胁主体表" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'接口资产'!$A$1:$K$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'数据资产'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'域属性表'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能资产'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'支持资产'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'接口资产'!$A$1:$G$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'边界接口表'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据资产'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'域属性表'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'功能资产'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'支持资产'!$A$1:$C$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'信任边界表'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'威胁主体表'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,13 +50,8 @@
     <font>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D4ED8"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,6 +113,16 @@
         <fgColor rgb="FFEBF8FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E7490"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB91C1C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,8 +173,8 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -166,8 +182,14 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,20 +556,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -578,39 +596,19 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>物理接口</t>
+          <t>目标功能</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>逻辑接口</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>网络域</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>目的</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>目标功能</t>
+          <t>所属边界接口</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SD01</t>
+          <t>BDF01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -620,54 +618,34 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>大数据平台</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>航线规划与任务配置数据（电子围栏/航线/备降点）</t>
+          <t>用户账号密码</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1.4G/4G/5G射频无线</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>私有协议/QUIC</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>空地数据链(D.2)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>飞行管理配置</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>F3</t>
+          <t>BI01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SD02</t>
+          <t>BDF02</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -677,54 +655,34 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>大数据平台</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>飞机任务与运行控制请求（起飞/悬停/恢复任务/备降等）</t>
+          <t>本地航线数据、电子围栏、备降点</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>CMD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>1.4G/4G/5G射频无线</t>
+          <t>F3,F4</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>私有协议/QUIC</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>空地数据链(D.2)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>飞行控制</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F5</t>
+          <t>BI01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SD03</t>
+          <t>BDF03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -734,12 +692,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>大数据平台</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>地面至机载语音通信数据</t>
+          <t>飞行数据</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -749,44 +707,24 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1.4G/4G/5G射频无线</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>私有协议/QUIC</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>空地数据链(D.2)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>语音通信</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>F8</t>
+          <t>BI01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SD04</t>
+          <t>BDF04</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>大数据平台</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -796,54 +734,34 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>飞机运行状态（遥测）</t>
+          <t>用户登录结果</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>1.4G/4G/5G射频无线</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>私有协议/QUIC</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>空地数据链(D.2)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>机载边界域→外部非信任域</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>状态监控</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>F7</t>
+          <t>BI01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SD05</t>
+          <t>BDF05</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>大数据平台</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -853,54 +771,34 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>飞机告警信息</t>
+          <t>航线、电子围栏、备降点数据</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1.4G/4G/5G射频无线</t>
+          <t>F3,F4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>私有协议/QUIC</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>空地数据链(D.2)</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>机载边界域→外部非信任域</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>告警通报</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>F5,F7</t>
+          <t>BI01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SD06</t>
+          <t>BDF06</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>大数据平台</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -910,121 +808,81 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>音视频数据（机载→地面）</t>
+          <t>航空器在线状态信息</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>1.4G/4G/5G射频无线</t>
+          <t>F7,F8</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>私有协议/QUIC</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>空地数据链(D.2)</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>机载边界域→外部非信任域</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>视频回传</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>F7</t>
+          <t>BI01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SD07</t>
+          <t>BDF07</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>大数据平台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>电子围栏/航线/备降点信息（ACU内部转发）</t>
+          <t>气象信息</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F3,F4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>机载边界域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>飞行管理配置</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>F3</t>
+          <t>BI01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SD08</t>
+          <t>BDF08</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>起飞/悬停/恢复任务/备降等控制指令（ACU转发）</t>
+          <t>链路切换指令</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1034,54 +892,34 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>机载边界域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>飞行控制执行</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>F5</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SD09</t>
+          <t>BDF09</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>飞机运行状态（ICC→ACU→地面）</t>
+          <t>遥控站状态</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1091,396 +929,256 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>状态上报</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>F7</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SD10</t>
+          <t>BDF10</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>飞机告警信息（ICC→ACU→地面）</t>
+          <t>航线、电子围栏、备降数据</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F3,F4</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>告警上报</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>F5,F7</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SD11</t>
+          <t>BDF11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>RTCM纠偏数据（差分导航）</t>
+          <t>音频数据</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>机载边界域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>差分导航修正</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>F4</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>SD12</t>
+          <t>BDF12</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>耳机</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>乘客语音输入</t>
+          <t>飞行控制类指令</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>CMD</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>有线耳机接口</t>
+          <t>F2,F8</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>音频协议</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>机载边界域内部</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>乘客通话</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>F8</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SD13</t>
+          <t>BDF13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>耳机</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>飞行机组语音输出</t>
+          <t>绑定航空器指令</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>CMD</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>有线耳机接口</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>音频协议</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>机载边界域内部</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>飞行机组通话</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>F8</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>SD16</t>
+          <t>BDF14</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>乘客语音（舱→链路）</t>
+          <t>ACU状态数据</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>UDP/RTSP</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>机载边界域内部</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>语音转发</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>F8</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SD19</t>
+          <t>BDF15</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>飞行机组语音（链路→舱）</t>
+          <t>航空器综合管理系统状态</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>UDP/RTSP</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>机载边界域内部</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>语音转发</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>F8</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>SD23</t>
+          <t>BDF16</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>障碍物类型/距离等状态信息</t>
+          <t>航空器飞行管理系统状态</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1490,111 +1188,71 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F3,F4,F7</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>探测与避让感知</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>F13</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SD24</t>
+          <t>BDF17</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>障碍物类型/距离告警及刹停告警建议</t>
+          <t>航空器飞行控制系统状态</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F2,F7</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>避障告警</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>F13</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>SD25</t>
+          <t>BDF18</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>姿态角/飞行速度等状态数据</t>
+          <t>航空器电推进系统状态</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1604,54 +1262,34 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F1,F7</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>机载航电域(D.4)</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>姿态同步</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>F4</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SD26</t>
+          <t>BDF19</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>转速等电机状态信息</t>
+          <t>航空器动力电池系统状态</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1661,54 +1299,34 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F1,F7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>动力状态监控</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2,F3,F7</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>SD27</t>
+          <t>BDF20</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>温度/电压/电流等电机状态信息</t>
+          <t>航空器高压配电系统状态</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1718,168 +1336,108 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F1,F7</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>动力健康监控</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>F1,F3,F7</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SD28</t>
+          <t>BDF21</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>转速/温度/电压/电流/故障代码告警</t>
+          <t>航空器电气系统状态</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F7,F9</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>动力故障告警</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2,F7</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>SD29</t>
+          <t>BDF22</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>转速控制指令</t>
+          <t>航空器伞降系统状态</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>CMD</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F5,F7</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>推力控制执行</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>F1,F2</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SD30</t>
+          <t>BDF23</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DCDC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>电源变换器状态信息</t>
+          <t>航空器导航系统状态</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1889,111 +1447,71 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F4,F7</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>电源状态监控</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>F2,F3,F7,F9</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>SD31</t>
+          <t>BDF24</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>DCDC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>电源变换器告警信息</t>
+          <t>航空器探测与避让系统状态</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F7,F13</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>电源故障告警</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>F2,F7,F9</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SD32</t>
+          <t>BDF25</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>LPDU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>低压配电盒状态信息</t>
+          <t>航空器音视频通信系统状态</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2003,225 +1521,145 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F6,F7</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>低压配电监控</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>F2,F3,F7,F9</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SD33</t>
+          <t>BDF26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>LPDU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>低压配电盒告警信息</t>
+          <t>航空器存储的航线数据</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F3,F4</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>低压配电告警</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>F2,F7,F9</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SD36</t>
+          <t>BDF27</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>HPDU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>高压配电盒状态信息</t>
+          <t>音视频数据</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F6,F8</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>高压配电监控</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2,F3,F7,F9</t>
+          <t>BI02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>SD37</t>
+          <t>BDF28</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>HPDU</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>高压配电盒告警信息</t>
+          <t>链路切换指令</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>CMD</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>高压配电告警</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>F1,F2,F7,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SD38</t>
+          <t>BDF29</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>HPDU</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>空地状态等信息下发</t>
+          <t>遥控站状态</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2231,396 +1669,256 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>高压配电控制</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>F1,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>SD38a</t>
+          <t>BDF30</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>LPDU</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>通道开关/复位指令</t>
+          <t>转发服务器状态</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>CMD</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>低压配电控制</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>F2,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SD38b</t>
+          <t>BDF31</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DCDC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>电源变换器复位指令</t>
+          <t>航线、电子围栏、备降数据</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CMD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F3,F4</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>电源复位控制</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>F2,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>SD39</t>
+          <t>BDF32</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>动力电池BMS状态信息</t>
+          <t>音频数据</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>电池状态监控</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>F1,F2,F3,F7,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SD40</t>
+          <t>BDF33</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>动力电池BMS告警信息</t>
+          <t>飞行控制类指令</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>CMD</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F2,F8</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>电池故障告警</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2,F7,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>SD41</t>
+          <t>BDF34</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>航空器空地状态信息</t>
+          <t>绑定航空器指令</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>CMD</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>空地状态同步</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>F1,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SD42</t>
+          <t>BDF35</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>高压上下电指令</t>
+          <t>ACU状态数据</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CMD</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>动力电池控制</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>F1,F9</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SD43</t>
+          <t>BDF36</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>高精度光纤组合导航</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>导航计算机/卫星接收机等状态信息</t>
+          <t>航空器综合管理系统状态</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -2630,225 +1928,145 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>导航系统健康监控</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SD43b</t>
+          <t>BDF37</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>高精度光纤组合导航</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>航向/姿态/速度/加速度/位置数据</t>
+          <t>航空器飞行管理系统状态</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F3,F4,F7</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>导航融合输入</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>SD44</t>
+          <t>BDF38</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>高精度光纤组合导航</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>航向/姿态/速度/加速度/GNSS位置告警</t>
+          <t>航空器飞行控制系统状态</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F2,F7</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>导航异常告警</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SD45</t>
+          <t>BDF39</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>高精度光纤组合导航</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>RTCM纠偏数据</t>
+          <t>航空器电推进系统状态</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F1,F7</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>差分导航修正</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>F4</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>SD46</t>
+          <t>BDF40</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MEMS组合导航</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>导航计算机/卫星接收机等状态信息</t>
+          <t>航空器动力电池系统状态</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2858,111 +2076,71 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F1,F7</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>备份导航状态</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SD47</t>
+          <t>BDF41</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MEMS组合导航</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>航向/姿态/速度/加速度/GNSS位置告警</t>
+          <t>航空器高压配电系统状态</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F1,F7</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>备份导航告警</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>F2,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>SD48</t>
+          <t>BDF42</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>MEMS组合导航</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>RTCM纠偏数据</t>
+          <t>航空器电气系统状态</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2972,54 +2150,34 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F7,F9</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>备份导航修正</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SD49</t>
+          <t>BDF43</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>无线电高度表</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>无线电高度表状态信息及相对高度数据</t>
+          <t>航空器伞降系统状态</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3029,111 +2187,71 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F5,F7</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>高度感知</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>SD50</t>
+          <t>BDF44</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>无线电高度表</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>相对高度告警信息</t>
+          <t>航空器导航系统状态</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F4,F7</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>低高度告警</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SD51</t>
+          <t>BDF45</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>伞降系统状态信息</t>
+          <t>航空器探测与避让系统状态</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3143,210 +2261,130 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F7,F13</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>伞降系统状态</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>F5,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>SD52</t>
+          <t>BDF46</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>伞降系统告警信息</t>
+          <t>航空器音视频通信系统状态</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F6,F7</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>伞降系统告警</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>F5,F7</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SD53</t>
+          <t>BDF47</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>开伞指令</t>
+          <t>航空器存储的航线数据</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>CMD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F3,F4</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>应急开伞控制</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>F5,F2</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>SD54</t>
+          <t>BDF48</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>转发服务器</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>加解锁指令</t>
+          <t>音视频数据</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>CMD</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F6,F8</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>机载控制域(D.5)</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域内部</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>伞降安保控制</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>F5</t>
+          <t>BI03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SD55</t>
+          <t>BDF49</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3356,396 +2394,256 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>NAVS</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>GNSS卫星数据（PES定位用）</t>
+          <t>GNSS定位与时间信息</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>卫星天线</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>射频信号</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>外部信号</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>应急定位</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>F4</t>
+          <t>BI04</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>SD56</t>
+          <t>BDF50</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>RTK</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>ACU配置文件</t>
+          <t>RTK差分修正数据</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>链路系统配置维护</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>F8</t>
+          <t>BI05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SD57</t>
+          <t>BDF51</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>环境视觉目标</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>DAAS</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>ACU管理软件</t>
+          <t>环境视觉图像数据</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>链路系统软件维护</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>F8</t>
+          <t>BI06</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>SD58</t>
+          <t>BDF52</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>环境激光反射目标</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>ACU</t>
+          <t>DAAS</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>ACU日志数据</t>
+          <t>激光雷达点云数据</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>机载边界域→外部非信任域</t>
-        </is>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>链路系统日志导出</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
-          <t>F10</t>
+          <t>BI07</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SD59</t>
+          <t>BDF53</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>环境音频源</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>AVCS</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>电机控制器配置文件</t>
+          <t>环境语音与音频输入数据、机舱环境音频数据</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F6,F8</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>动力系统配置维护</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2</t>
+          <t>BI08</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>SD60</t>
+          <t>BDF54</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>环境视频目标</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>AVCS</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>电机控制器管理软件/引导加载软件</t>
+          <t>舱内视频采集数据</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F6,F8</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>动力系统软件维护</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>F1,F2</t>
+          <t>BI09</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>SD61</t>
+          <t>BDF55</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>环境视频目标</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>AVCS</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>电池管理系统管理软件/引导加载软件</t>
+          <t>下视环境视频数据</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>F6,F8</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>标准CAN</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>电池系统软件维护</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>F1,F3,F9</t>
+          <t>BI09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>SD62</t>
+          <t>BDF56</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3755,54 +2653,34 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>ICP</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>综合控制计算机配置/诊断/控制指令</t>
+          <t>软件加载数据</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>核心计算机配置维护</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>F1,F2,F3</t>
+          <t>BI10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SD63</t>
+          <t>BDF57</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3812,69 +2690,49 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ICC/BICC</t>
+          <t>ICP</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>综合控制计算机管理软件/引导加载软件</t>
+          <t>参数配置数据</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F2,F3,F4,F11,F12</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>核心计算机软件维护</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2,F3</t>
+          <t>BI10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>SD64</t>
+          <t>BDF58</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
           <t>地面维护设备</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>ICC/BICC</t>
-        </is>
-      </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>日志/运行记录/备份导出数据</t>
+          <t>诊断数据、日志数据</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -3884,96 +2742,56 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F10,F11</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>机载核心信任域→外部非信任域</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>核心计算机数据导出</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>F10</t>
+          <t>BI10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SD65</t>
+          <t>BDF59</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
           <t>地面维护设备</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>ICC/BICC</t>
-        </is>
-      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>BICC管理软件/引导加载软件</t>
+          <t>软件版本与配置状态</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>备份计算机软件维护</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2,F3</t>
+          <t>BI10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>SD66</t>
+          <t>BDF60</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3983,12 +2801,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>探测与避让系统配置文件</t>
+          <t>配置文件</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -3998,39 +2816,19 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>USB3.0</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>探测避让系统配置</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F11</t>
+          <t>BI11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SD67</t>
+          <t>BDF61</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4040,111 +2838,71 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>探测与避让系统日志</t>
+          <t>管理软件</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>USB3.0</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>机载核心信任域→外部非信任域</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>探测避让日志导出</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>F10</t>
+          <t>BI11</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>SD68</t>
+          <t>BDF62</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
           <t>地面维护设备</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>AVCS</t>
-        </is>
-      </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>音视频通信系统配置/诊断/控制指令</t>
+          <t>日志</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>RS232/ETH</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>音视频系统配置维护</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>F7,F8</t>
+          <t>BI11</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SD69</t>
+          <t>BDF63</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4154,54 +2912,34 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>AVCS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>音视频通信系统管理软件/引导加载软件</t>
+          <t>配置文件</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>RS232/ETH</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载边界域</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>音视频系统软件维护</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>F7,F8</t>
+          <t>BI12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>SD71</t>
+          <t>BDF64</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4211,12 +2949,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>导航系统</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>导航系统（光纤/MEMS组合导航）管理软件/引导加载软件</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -4226,39 +2964,19 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>导航系统软件维护</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F4</t>
+          <t>BI12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SD72</t>
+          <t>BDF65</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4268,72 +2986,640 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>导航系统</t>
+          <t>PACKS</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>导航系统软件维护配置</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>RS422</t>
+          <t>F1,F9</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>私有协议</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>地面维护域(D.6)</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>外部非信任域→机载核心信任域</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>导航系统参数维护</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>F2,F3,F4</t>
+          <t>BI13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>BDF66</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>管理软件/引导加载软件</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>LOAD</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>F1,F9</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>BI14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>BDF67</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>配置文件</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>F11,F13</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>BI15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>BDF68</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>BI15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>BDF69</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>配置/诊断数据</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>F7,F8</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>BI16</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>BDF70</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>管理软件/引导加载软件</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>LOAD</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>F6,F8</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>BI16</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>BDF71</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>AVCS运行数据备份</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>F10</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>BI16</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>BDF72</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>管理软件/引导加载软件</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>LOAD</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>BI17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>BDF73</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>软件维护配置</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>BI17</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>BDF74</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>日志</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>F5,F10</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>BI18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>BDF75</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>引导加载软件</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>LOAD</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>F5,F11</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>BI18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>BDF76</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>调试计算机</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>调试控制数据</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>F2,F11</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>BI19</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>BDF77</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>UPS运行状态</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>BI20</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>BDF78</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>操控员</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>人工控制输入</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>F2,F8</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>BI21</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>BDF79</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>操控员</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>航空器运行状态显示信息</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>F7,F8</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>BI21</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>BDF80</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>操控员</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>告警显示信息</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>F5,F7,F12</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>BI21</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>BDF81</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>操控员</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>音视频与任务显示信息</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>F6,F7,F8</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>BI21</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
           <t>以下是样例，请勿填写此行以下内容</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="3" t="inlineStr"/>
-      <c r="K67" s="3" t="inlineStr"/>
+      <c r="B83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr"/>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K67"/>
+  <autoFilter ref="A1:G83"/>
   <dataValidations count="1">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CMD,CONFIG,STATE,DATA,LOAD,ALERT"</formula1>
+      <formula1>"CMD,CONFIG,STATE,DATA,LOAD,ALERT,SENSOR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4346,56 +3632,1131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>接口编号</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>接口类别</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>外部实体</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>边界接入对象</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>物理互连类型</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>逻辑协议</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>方向性</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>安保边界</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>接口说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BI01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>网络通信</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>大数据平台</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>云业务接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>BI02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>网络通信</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>转发服务器</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>QUIC</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>外部链路与业务中继接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BI03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>网络通信</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>转发服务器</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4G/5G</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>QUIC</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>空地链路中继接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>BI04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>导航输入</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>GNSS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>GNSS信号</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>单向</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>GNSS导航输入接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>BI05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>导航输入</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>RTK服务</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>RS422</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>单向</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>RTK差分修正输入接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>BI06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>感知输入</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>开放环境</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>摄像头链路</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>图像数据流</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>单向</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>视觉感知输入接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BI07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>感知输入</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>开放环境</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>激光雷达</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>点云数据流</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>单向</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>激光雷达输入接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>BI08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>感知输入</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>开放环境</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>麦克风</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>音频数据流</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>单向</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>环境音频输入接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BI09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>感知输入</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>开放环境</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>摄像头</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>视频数据流</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>单向</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>环境视频输入接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>BI10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>CAN/ETH</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>ICP维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>BI11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>DLS维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>BI12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>CAN协议</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>EPS维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>BI13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CAN协议</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>PACKS维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>BI14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>CAN协议</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>HVDS维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>BI15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>USB3.0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>DAAS维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>BI16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>RS232/ETH</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>AVCS维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BI17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>RS422</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>NAVS维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>BI18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>维护接入</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>RS232</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>PES维护接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BI19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>调试接入</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>调试设备</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>RS422</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>RCS调试接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>BI20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>外围设备接口</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>RS232</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>私有协议</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>电源监控接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BI21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>人机交互</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>操控员</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>人机交互设备</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>HMI协议</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>操控员交互接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>以下是样例，请勿填写此行以下内容</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>数据名称</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>数据类型</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>数据流类型</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>对应接口</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>所属域</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>目标功能</t>
         </is>
@@ -4422,11 +4783,7 @@
           <t>LOAD</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>SD63</t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4434,7 +4791,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合控制计算机(ICC)主应用软件</t>
+          <t>综合控制计算机(ICC/IMS)主应用软件</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4464,11 +4821,7 @@
           <t>LOAD</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>SD65</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4506,11 +4859,7 @@
           <t>LOAD</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>SD60</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4518,7 +4867,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>电机控制器(MCU)管理软件</t>
+          <t>电机控制器(MCU/EPS)管理软件</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -4548,11 +4897,7 @@
           <t>LOAD</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>SD61</t>
-        </is>
-      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4560,7 +4905,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>电池管理系统(BMS)全功能软件</t>
+          <t>电池管理系统(BMS/PACKS)全功能软件</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -4590,11 +4935,7 @@
           <t>LOAD</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>SD71</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4632,11 +4973,7 @@
           <t>CONFIG</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>SD66</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4649,7 +4986,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>F2,F3,F11</t>
+          <t>F2,F3,F13</t>
         </is>
       </c>
     </row>
@@ -4674,11 +5011,7 @@
           <t>CONFIG</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>SD62</t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4716,11 +5049,7 @@
           <t>CONFIG</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>SD59</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>D.6</t>
@@ -4740,607 +5069,19 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DA.09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>FCS_CMD</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>飞行控制指令</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>CMD</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>SD29</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>D.5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>ICC→MCU转速控制指令</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>DA.10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>BMS_PWR_CMD</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>上下电控制指令</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>CMD</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>SD42</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>D.5</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>ICC→BMS高压上下电指令</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>F1,F9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>DA.11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>PES_OPEN_CMD</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>开伞控制指令</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>CMD</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>SD53</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>D.5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>ICC→PES开伞指令（应急）</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>F5,F2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>DA.12</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>RCS_CTRL_CMD</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>运行控制请求</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>CMD</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>SD02</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>D.2</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>RCS→ACU任务与运行控制请求</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>DA.13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>INS_NAV_DATA</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>导航融合数据</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>SD43,SD43b</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>D.5</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>高精度光纤组合导航 航向/姿态/速度/位置</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>DA.14</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>MEMS_NAV_DATA</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>备份导航数据</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>SD46</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>D.5</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>MEMS组合导航 航向/姿态/速度/位置</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F4,F7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>DA.15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>GNSS_SIGNAL</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>GNSS导航信号</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>SD55</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>D.1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>GNSS卫星定位/时间信号（开放环境）</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>DA.16</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>RTCM_DATA</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>差分纠偏数据</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>SD11,SD48</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>D.4</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>RTK差分纠偏数据</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>DA.17</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>AC_STATE</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>飞机运行状态</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>SD04,SD09</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>D.2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>飞机综合运行状态遥测数据</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>F7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>DA.18</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>MCU_STATE</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>电机状态数据</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>SD26,SD27</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>D.5</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>MCU转速/温度/电压/电流状态</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>F1,F3,F7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>DA.19</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>BMS_STATE</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>电池状态数据</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>SD39</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>D.5</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>动力电池BMS状态信息</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>F1,F2,F3,F9</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>DA.20</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>MISSION_CFG</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>任务配置数据</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>SD01,SD07</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>D.2</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>航线/电子围栏/备降点配置</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>DA.21</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ICC_LOG</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>诊断日志数据</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>SD64</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>D.6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>ICC运行日志/故障记录/备份数据</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>F10,F11</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>DA.22</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>ACU_LOG</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>链路系统日志</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>SD58</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>D.6</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>ACU运行日志数据</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>F10</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
           <t>以下是样例，请勿填写此行以下内容</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:H10"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CMD,CONFIG,STATE,DATA,LOAD,ALERT"</formula1>
@@ -5350,7 +5091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5367,27 +5108,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>域编号</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>域名称</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>信任程度</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>安全域</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -5443,7 +5184,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ACU与地面GCU/转发服务器间的射频通信链路（1.4G/4G/5G）。可能经过公网/运营商网络。</t>
+          <t>DLS与地面RCS间的射频通信链路（1.4G/4G/5G）。可能经过公网/运营商网络。</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5211,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ACU/GCU/AVCS/CCU等机载边界与通信系统，承担对外音视频业务及链路接入功能。</t>
+          <t>DLS/AVCS等机载边界与通信系统，承担对外音视频业务及链路接入功能。</t>
         </is>
       </c>
     </row>
@@ -5497,7 +5238,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ACU/CCU/DAAS/NAVS等航空电子设备。部分依赖开放环境输入（GNSS/DAA），需一致性校验。</t>
+          <t>IMS/DAAS/NAVS等航空电子设备。部分依赖开放环境输入（GNSS/DAA），需一致性校验。</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5265,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ICP(ICC/BICC)/FCS/FMS/IMS/EPS/ES/PACKS/HVDS/NAVS/DAAS/PES。直接决定飞行安全，内部通信假定在受控环境。</t>
+          <t>IMS(ICC/BICC)/FCS/FMS/EPS/ES/PACKS/HVDS/PES。直接决定飞行安全，内部通信假定在受控环境。</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5595,17 +5336,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>功能资产名称</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>资产说明</t>
         </is>
@@ -5743,7 +5484,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>F8: DLS链路管理/音视频通信（ACU/AVCS）</t>
+          <t>F8: DLS链路管理/音视频通信（AVCS）</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5501,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>F9: 供配电管理（ES/BMS/HVDS/PACKS）</t>
+          <t>F9: 供配电管理（ES/PACKS/HVDS）</t>
         </is>
       </c>
     </row>
@@ -5843,137 +5584,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C15"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>交联接口</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ASA.01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RCS遥控站终端</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>SD01, SD02, SD03, SD04, SD05, SD06</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>ASA.02</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>GCU地面通信单元</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>SD01, SD02, SD04, SD05</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ASA.03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>转发服务器</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>SD01, SD02, SD04, SD05</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ASA.04</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>GNSS/RTK服务</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SD55</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ASA.05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>SD56, SD57, SD59, SD60, SD61, SD62, SD63, SD66, SD71</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>以下是样例，请勿填写此行以下内容</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5984,7 +5594,339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>交联接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ASA.01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>ASA.02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>大数据平台</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ASA.03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>转发服务器</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ASA.04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ASA.05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>GNSS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ASA.06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ASA.07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>RTK</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ASA.08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>环境视觉目标</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ASA.09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ASA.10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>环境激光反射目标</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ASA.11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>环境音频源</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ASA.12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ASA.13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>环境视频目标</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ASA.14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ASA.15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ICP</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ASA.16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ASA.17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ASA.18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ASA.19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ASA.20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>调试计算机</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ASA.21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>ASA.22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>操控员</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>以下是样例，请勿填写此行以下内容</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5995,217 +5937,646 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>数据流类型</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>主要STRIDE类别</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>典型攻击模式(ZG-ONE TC)</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>典型攻击模式</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>安保措施方向</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>FHA严重度参考</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="52" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>CMD</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Spoofing + Tampering</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>TC1未授权指令注入 / TC2指令篡改 / TC3指令重放
-TC11推力指令异常 / TC14非法上下电 / TC15伞降误触发</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>双向认证(双向TLS或等效) + 完整性保护(MAC/签名)
-序列号+时间窗校验 + 运行状态门控</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>未授权指令注入/篡改/重放；推力/上下电/伞降误触发</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>双向认证 + 完整性保护(MAC/签名) + 序列号/时间窗 + 运行状态门控</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Catastrophic / Hazardous</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="52" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>CONFIG</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Tampering</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>TC4配置数据恶意修改(航线/围栏)
-TC9未授权维护访问 + 参数篡改</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>签名 + 语义约束检查 + 版本控制
-强认证 + RBAC访问控制</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>配置数据恶意修改(航线/围栏)；未授权维护参数篡改</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>签名 + 语义约束检查 + 版本控制 + 强认证/RBAC</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Hazardous / Major</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>LOAD</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Tampering</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>TC8恶意软件加载(维护接口)
-TC9未授权维护访问</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Secure Boot + 软件签名验证
-完整性链 + 强认证 + RBAC</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>恶意软件加载(维护接口)；未授权维护访问</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Secure Boot + 软件签名验证 + 完整性链 + 强认证/RBAC</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Catastrophic</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>STATE</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Spoofing</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>TC5 GNSS欺骗 / TC7 RTCM注入
-TC12 MCU状态反馈伪造 / TC20导航融合异常</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>多源融合一致性校验 + 异常检测
-可信度评估 + INS/RAIM冗余</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>状态/遥测伪造；导航融合异常</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>多源融合一致性校验 + 异常检测 + 冗余</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Major / Hazardous</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>ALERT</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Tampering + DenialOfService</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>TC16控制闭环DoS(总线阻塞)
-TC18避障告警抑制 / TC22告警信息篡改</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>完整性保护 + 实时调度 + 带宽隔离
-告警超时检测 + 失效安全策略</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>告警抑制/篡改；总线阻塞DoS</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>完整性保护 + 实时调度/带宽隔离 + 告警超时检测</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Hazardous / Catastrophic</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>InformationDisclosure</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>TC21状态数据泄露 / TC23视频流劫持
-维护日志导出数据暴露</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>加密传输(TLS) + 访问控制
-流媒体加密</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>状态/视频数据泄露；日志导出暴露</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>加密传输(TLS) + 访问控制 + 流媒体加密</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Minor / Major</t>
         </is>
       </c>
     </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>SENSOR</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Spoofing + Tampering</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>GNSS欺骗/干扰；探测/感知输入伪造</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>多源一致性 + 物理合理性约束 + 冗余传感器交叉验证</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Major / Hazardous</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>边界编号</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>边界名称</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>边界说明</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>覆盖域</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>相关威胁主体</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>是否进入内部传播</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SB-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>外部网络与通信边界</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>系统与外部网络、云平台、通信基础设施及操控终端之间的数据交换边界。</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>D.1;D.2;D.3</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>TA-E-01;TA-E-02;TA-I-01</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SB-02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>开放环境输入边界</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>系统接收来自开放环境的导航、感知和探测信息的边界。</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>D.1;D.4</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>TA-E-03;TA-E-04</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SB-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>维护与物理接入边界</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>系统软件加载、参数配置、调试维护和设备接入边界。</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>D.6;D.5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TA-E-05;TA-I-02;TA-I-03;TA-I-04</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>以下是样例，请勿填写此行以下内容</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="F2:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>主体编号</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TA-E-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>远程网络攻击者</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>外部</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>经公网/运营商网络对空地数据链及云平台发起远程攻击。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>TA-E-02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>通信链路攻击者</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>外部</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>针对1.4G/4G/5G射频链路的中间人/重放/注入攻击。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TA-E-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>GNSS欺骗/干扰者</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>外部</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>对GNSS卫星信号进行欺骗或干扰，影响导航定位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>TA-E-04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>开放环境输入伪造者</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>外部</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>伪造探测/感知/导航等开放环境输入数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TA-E-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>恶意维护人员/设备</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>外部</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>通过维护接口加载恶意软件或篡改参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TA-I-01</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>受感染地面终端</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>内部</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>被攻陷的RCS/转发服务器成为内部攻击跳板。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TA-I-02</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>维护误操作</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>内部</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>维护人员误操作导致配置或软件异常。</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>[说明] 此表为参考，不参与系统解析。接口资产/数据资产填写数据流类型后，系统按此映射自动生成STRIDE威胁节点及攻击路径分析。威胁状态编号(TC)参见 ZG-ONE 202605150007 第6章。</t>
-        </is>
-      </c>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TA-I-03</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>供应链植入</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>第三方</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>供应链环节植入的后门或被篡改的组件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TA-I-04</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>内部越权访问</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>内部</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>内部人员越权访问或滥用维护/管理权限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>以下是样例，请勿填写此行以下内容</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A9:E9"/>
-  </mergeCells>
+  <autoFilter ref="A1:D11"/>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"外部,内部,第三方"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/资产清单_v3_可导入.xlsx
+++ b/docs/资产清单_v3_可导入.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STRIDE映射表" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="信任边界表" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="威胁主体表" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统数据流表" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'接口资产'!$A$1:$G$83</definedName>
@@ -23,9 +24,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据资产'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'域属性表'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'功能资产'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'支持资产'!$A$1:$C$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'支持资产'!$A$1:$E$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'信任边界表'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'威胁主体表'!$A$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'系统数据流表'!$A$1:$F$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,7 +53,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +125,11 @@
         <fgColor rgb="FFB91C1C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F766E"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -150,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,6 +196,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3626,6 +3636,1838 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>数据流编号</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>产生者</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>用户</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>数据流类型</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>目标功能</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SDF01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>电子围栏、航线、备降点信息</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SDF02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>起飞、悬停、恢复任务、备降、上下电、低压配电盒通道开关及复位、电源变换器复位等控制指令</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SDF03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>飞行机组语音</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SDF04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>飞机运行状态</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SDF05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>飞机告警信息</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SDF06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>音视频数据</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SDF07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>电子围栏、航线、备降点信息</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SDF08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>起飞、悬停、恢复任务、备降、上下电、低压配电盒通道开关及复位、电源变换器复位等控制指令</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SDF09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>飞机运行状态</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SDF10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>飞机告警信息</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SDF11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>乘客语音</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SDF12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>舱内摄像头视频流</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SDF13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>下视摄像头视频流</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SDF14</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>飞行机组语音</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SDF15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>DLS</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>叠加探测信息的视频流</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SDF16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>障碍物类型、距离等状态</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SDF17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>障碍物类型、距离等告警；刹停告警建议</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SDF18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>姿态角、飞行速度等数据</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SDF19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>转速等状态信息</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>F1,F2,F3,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SDF20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>温度、电压、电流等状态信息</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>F1,F3,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SDF21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>转速、温度、电压、电流、故障代码等告警信息</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>F1,F2,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SDF22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>转速控制指令</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>F1,F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SDF23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>电源变换器、低压配电盒、应急配电盒、应急电池状态信息</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F7,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SDF24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>电源变换器、低压配电盒、应急配电盒、应急电池告警信息</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>F2,F7,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SDF25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>复位/通道通断指令</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>F2,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SDF26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>高压配电盒状态信息</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>F1,F2,F3,F7,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SDF27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>高压配电盒告警信息</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>F1,F2,F7,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>SDF28</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>空地状态、电机电压、动力电池电压电流值等信息</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>F1,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SDF29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>电池电压、电流、温度等状态信息</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>F1,F2,F3,F7,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SDF30</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>电池电压、电流、温度等告警信息</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>F1,F2,F7,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SDF31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>高压上下电指令</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>F1,F2,F3,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>SDF32</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>航空器空地状态、高压配电盒支路继电器状态</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>F1,F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SDF33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>导航计算机、卫星接收机、卫星天线、三轴陀螺、三轴加速度计等状态信息</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F4,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>SDF34</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>航向、姿态、速度、加速度、位置等数据信息</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>F2,F3,F4,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SDF35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>航向、姿态、速度、加速度、GNSS位置等告警信息</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F4,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>SDF36</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>NAVS</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>RTCM纠偏数据</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>F2,F3,F4,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SDF37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>状态信息</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>SDF38</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>告警信息</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SDF39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>开伞指令</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>F5,F2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>SDF40</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PES</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>加解锁指令</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SDF41</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>导航数据</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F4,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>SDF42</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>备降点数据</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>F2,F3,F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SDF43</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>电子围栏数据</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>SDF44</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>应急降落微调指令数据</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>F2,F3,F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SDF45</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>转速控制指令</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>F1,F2,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>SDF46</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>内外环控制量，当前飞行状态及模式</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>F2,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SDF47</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>飞行包线告警信息，电子围栏告警信息</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>SDF48</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>导航数据</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>F3,F4,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SDF49</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>探测与避让系统数据</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>F3,F7,F13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>SDF50</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>飞行航线数据</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>F3,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>SDF51</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>动力电池电量、功率数据</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>F1,F3,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>SDF52</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>待飞时间和待飞航程，剩余续航时间和续航里程</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>F2,F3,F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SDF53</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>当前飞行状态</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F5,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>SDF54</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>避让告警信息</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>F2,F3,F5,F7,F13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SDF55</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>FMS</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>FCS</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>制导指令</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>F2,F3,F7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>以下是样例，请勿填写此行以下内容</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="3" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F57"/>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CMD,CONFIG,STATE,DATA,LOAD,ALERT,SENSOR"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5594,12 +7436,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -5618,6 +7462,16 @@
           <t>交联接口</t>
         </is>
       </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>安全域</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>关键性</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5631,6 +7485,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -5644,6 +7508,16 @@
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5657,6 +7531,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5670,6 +7554,16 @@
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5683,6 +7577,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -5696,6 +7600,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5709,6 +7623,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -5722,6 +7646,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5735,6 +7669,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5748,6 +7692,16 @@
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5761,6 +7715,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -5774,6 +7738,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5787,6 +7761,16 @@
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -5800,6 +7784,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5813,6 +7807,16 @@
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -5826,6 +7830,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5839,6 +7853,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -5852,6 +7876,16 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5865,6 +7899,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -5878,6 +7922,16 @@
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5891,6 +7945,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5904,6 +7968,16 @@
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5913,9 +7987,19 @@
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C24"/>
+  <autoFilter ref="A1:E24"/>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Internal,External,DMZ,Shared"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
